--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashna\eclipse-workspace\7RMartSuperMarket\src\main\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B8C4E4-FF8F-4EA1-B39D-350FA16AC9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{2B67E28C-5EFC-4843-9554-AF1A4B2C7666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
     <sheet name="Adminpagetest" sheetId="2" r:id="rId2"/>
     <sheet name="Managetest" sheetId="3" r:id="rId3"/>
     <sheet name="Newstest" sheetId="4" r:id="rId4"/>
+    <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:N3"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>admin</t>
   </si>
@@ -560,4 +557,30 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFA6D754-5942-4784-80CB-4350EA43C166}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{2B67E28C-5EFC-4843-9554-AF1A4B2C7666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{61C67CAE-13B5-4DB0-AD48-70A9F17F2CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,21 +15,10 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:N3"/>
+  <oleSize ref="A1:M10"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{61C67CAE-13B5-4DB0-AD48-70A9F17F2CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{C8F9A382-05B3-458D-8A8A-7D74E6608FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:M10"/>
+  <oleSize ref="A1:M5"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,10 +60,10 @@
     <t>hihello</t>
   </si>
   <si>
-    <t>shivambllbbba</t>
-  </si>
-  <si>
     <t>teacup</t>
+  </si>
+  <si>
+    <t>sanju samsonchennaisuperkings</t>
   </si>
 </sst>
 </file>
@@ -489,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -516,7 +516,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{C8F9A382-05B3-458D-8A8A-7D74E6608FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{8D865FEC-22AF-4B84-907C-E0B441D77B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:M5"/>
+  <oleSize ref="A1:L5"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,10 +60,10 @@
     <t>hihello</t>
   </si>
   <si>
-    <t>teacup</t>
-  </si>
-  <si>
     <t>sanju samsonchennaisuperkings</t>
+  </si>
+  <si>
+    <t>teacupsssss</t>
   </si>
 </sst>
 </file>
@@ -489,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -516,7 +516,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{8D865FEC-22AF-4B84-907C-E0B441D77B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{A45FEBB6-ED26-42E1-9B5C-2BF513DE6B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="1" activeTab="1" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:L5"/>
+  <oleSize ref="A1:F4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,10 +60,10 @@
     <t>hihello</t>
   </si>
   <si>
-    <t>sanju samsonchennaisuperkings</t>
-  </si>
-  <si>
     <t>teacupsssss</t>
+  </si>
+  <si>
+    <t>sanju sadmsonchennaisuperkings</t>
   </si>
 </sst>
 </file>
@@ -489,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -516,7 +516,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{A45FEBB6-ED26-42E1-9B5C-2BF513DE6B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{16857945-93AB-4BD9-893C-D48762019117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="1" activeTab="1" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:F4"/>
+  <oleSize ref="A1:N9"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,10 +60,10 @@
     <t>hihello</t>
   </si>
   <si>
-    <t>teacupsssss</t>
-  </si>
-  <si>
-    <t>sanju sadmsonchennaisuperkings</t>
+    <t>sanju sjjadmsonchennaisuperkings</t>
+  </si>
+  <si>
+    <t>solareclipse</t>
   </si>
 </sst>
 </file>
@@ -489,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -516,7 +516,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{16857945-93AB-4BD9-893C-D48762019117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B2DC2C80-7D64-4E20-A0E1-831AC2E533BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:N9"/>
+  <oleSize ref="A1:L4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -63,7 +63,7 @@
     <t>sanju sjjadmsonchennaisuperkings</t>
   </si>
   <si>
-    <t>solareclipse</t>
+    <t>solareclipse2026</t>
   </si>
 </sst>
 </file>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B2DC2C80-7D64-4E20-A0E1-831AC2E533BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{D6CE1623-BA2C-4FF7-B0A7-5A96F3A3E0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:L4"/>
+  <oleSize ref="A1:M6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,13 +57,13 @@
     <t>message</t>
   </si>
   <si>
-    <t>hihello</t>
-  </si>
-  <si>
     <t>sanju sjjadmsonchennaisuperkings</t>
   </si>
   <si>
-    <t>solareclipse2026</t>
+    <t>solareclipse2026jjj</t>
+  </si>
+  <si>
+    <t>hihellohi</t>
   </si>
 </sst>
 </file>
@@ -489,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -516,7 +516,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -540,7 +540,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{D6CE1623-BA2C-4FF7-B0A7-5A96F3A3E0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{FBB7F561-50CB-46F2-8A0B-10D6426E1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:M6"/>
+  <oleSize ref="A1:L6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,10 +60,10 @@
     <t>sanju sjjadmsonchennaisuperkings</t>
   </si>
   <si>
-    <t>solareclipse2026jjj</t>
-  </si>
-  <si>
     <t>hihellohi</t>
+  </si>
+  <si>
+    <t>solareclipse2026jjjhh</t>
   </si>
 </sst>
 </file>
@@ -516,7 +516,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -540,7 +540,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{FBB7F561-50CB-46F2-8A0B-10D6426E1DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1A8B79E2-40E9-47E5-B9C2-3B73FFB6371E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
@@ -63,7 +63,7 @@
     <t>hihellohi</t>
   </si>
   <si>
-    <t>solareclipse2026jjjhh</t>
+    <t>jupiter</t>
   </si>
 </sst>
 </file>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1A8B79E2-40E9-47E5-B9C2-3B73FFB6371E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1C99351C-667E-4BE0-9EA6-FCDBEAEBF695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:L6"/>
+  <oleSize ref="A1:M9"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -63,7 +63,7 @@
     <t>hihellohi</t>
   </si>
   <si>
-    <t>jupiter</t>
+    <t>jupitergftfht</t>
   </si>
 </sst>
 </file>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1C99351C-667E-4BE0-9EA6-FCDBEAEBF695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{A32638BA-CF7C-435F-ABC2-43A03D60168F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:M9"/>
+  <oleSize ref="A1:K9"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -63,7 +63,7 @@
     <t>hihellohi</t>
   </si>
   <si>
-    <t>jupitergftfht</t>
+    <t>jupitergftfhtgggsgg</t>
   </si>
 </sst>
 </file>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{A32638BA-CF7C-435F-ABC2-43A03D60168F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{167AEEDA-30E7-41E5-8717-E386EAA1A67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:K9"/>
+  <oleSize ref="A1:L9"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,9 +45,6 @@
     <t>password2</t>
   </si>
   <si>
-    <t>hihello123</t>
-  </si>
-  <si>
     <t>username1</t>
   </si>
   <si>
@@ -57,13 +54,16 @@
     <t>message</t>
   </si>
   <si>
-    <t>sanju sjjadmsonchennaisuperkings</t>
-  </si>
-  <si>
-    <t>hihellohi</t>
-  </si>
-  <si>
-    <t>jupitergftfhtgggsgg</t>
+    <t>chocolatepumkins</t>
+  </si>
+  <si>
+    <t>hihelloworld</t>
+  </si>
+  <si>
+    <t>mahendrasingh</t>
+  </si>
+  <si>
+    <t>hihello123345</t>
   </si>
 </sst>
 </file>
@@ -464,7 +464,8 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -475,7 +476,7 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
         <v>5</v>
@@ -489,10 +490,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -511,12 +512,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -535,12 +536,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{167AEEDA-30E7-41E5-8717-E386EAA1A67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{9701BC67-76DC-4478-B58E-523378635436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:L9"/>
+  <oleSize ref="A1:K4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,9 +54,6 @@
     <t>message</t>
   </si>
   <si>
-    <t>chocolatepumkins</t>
-  </si>
-  <si>
     <t>hihelloworld</t>
   </si>
   <si>
@@ -64,6 +61,9 @@
   </si>
   <si>
     <t>hihello123345</t>
+  </si>
+  <si>
+    <t>chocolatepumkinscool</t>
   </si>
 </sst>
 </file>
@@ -490,10 +490,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +506,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
     <col min="3" max="3" width="16.90625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -517,7 +517,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +541,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{9701BC67-76DC-4478-B58E-523378635436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{52FC0E09-D956-4EE7-BD71-C41762E8780D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
@@ -63,7 +63,7 @@
     <t>hihello123345</t>
   </si>
   <si>
-    <t>chocolatepumkinscool</t>
+    <t>chocolatepumkinscools</t>
   </si>
 </sst>
 </file>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{52FC0E09-D956-4EE7-BD71-C41762E8780D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{969E7052-1F15-4BCD-A6AA-EEE681E98377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:K4"/>
+  <oleSize ref="A1:M4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,16 +54,16 @@
     <t>message</t>
   </si>
   <si>
-    <t>hihelloworld</t>
-  </si>
-  <si>
-    <t>mahendrasingh</t>
-  </si>
-  <si>
     <t>hihello123345</t>
   </si>
   <si>
-    <t>chocolatepumkinscools</t>
+    <t>sunchoclate</t>
+  </si>
+  <si>
+    <t>mahendrasinghdhonic</t>
+  </si>
+  <si>
+    <t>hihelloworld2026</t>
   </si>
 </sst>
 </file>
@@ -464,7 +464,7 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="14.54296875" customWidth="1"/>
+    <col min="3" max="3" width="18.7265625" customWidth="1"/>
     <col min="4" max="4" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -490,10 +490,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -530,7 +530,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -541,7 +541,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{969E7052-1F15-4BCD-A6AA-EEE681E98377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7BF42A84-7AAB-4930-9989-BFE1DE715005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:M4"/>
+  <oleSize ref="A1:L4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,16 +54,16 @@
     <t>message</t>
   </si>
   <si>
-    <t>hihello123345</t>
-  </si>
-  <si>
     <t>sunchoclate</t>
   </si>
   <si>
-    <t>mahendrasinghdhonic</t>
-  </si>
-  <si>
     <t>hihelloworld2026</t>
+  </si>
+  <si>
+    <t>shivamcsk</t>
+  </si>
+  <si>
+    <t>hihello12354345</t>
   </si>
 </sst>
 </file>
@@ -493,7 +493,7 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +541,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7BF42A84-7AAB-4930-9989-BFE1DE715005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DFEF0FC2-819E-4B9C-B20A-6C70EA72ED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loginpagetest" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Hometest" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:L4"/>
+  <oleSize ref="A1:M4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,16 +54,16 @@
     <t>message</t>
   </si>
   <si>
-    <t>sunchoclate</t>
-  </si>
-  <si>
-    <t>hihelloworld2026</t>
-  </si>
-  <si>
-    <t>shivamcsk</t>
-  </si>
-  <si>
-    <t>hihello12354345</t>
+    <t>shivamcskdubey</t>
+  </si>
+  <si>
+    <t>hihellocsk</t>
+  </si>
+  <si>
+    <t>sunchoclatepudding</t>
+  </si>
+  <si>
+    <t>hihelloworld2026Y</t>
   </si>
 </sst>
 </file>
@@ -465,7 +465,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="18.7265625" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -490,10 +490,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +541,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectSuperMarket/src/main/resources/Book1.xlsx
+++ b/ProjectSuperMarket/src/main/resources/Book1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DFEF0FC2-819E-4B9C-B20A-6C70EA72ED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{46EDDA91-CFC3-42C9-86CB-E2A96AF88039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{72A6C1A5-5943-4E36-AA4D-7B07BB5FD9C0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>admin</t>
   </si>
@@ -64,6 +64,18 @@
   </si>
   <si>
     <t>hihelloworld2026Y</t>
+  </si>
+  <si>
+    <t>searchname</t>
+  </si>
+  <si>
+    <t>ashnaprk</t>
+  </si>
+  <si>
+    <t>searchmessage</t>
+  </si>
+  <si>
+    <t>March 24th 2026</t>
   </si>
 </sst>
 </file>
@@ -461,14 +473,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2393F9-7B3C-4082-82B1-B370CE8E2D24}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="18.7265625" customWidth="1"/>
     <col min="4" max="4" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -481,8 +493,11 @@
       <c r="D1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -494,6 +509,9 @@
       </c>
       <c r="D2" t="s">
         <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -527,21 +545,28 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC59A529-5AB6-4BD4-A7CF-3018D5A8C39E}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
